--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92658</v>
+        <v>92664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95692</v>
+        <v>95698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92664</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95698</v>
+        <v>95701</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95701</v>
+        <v>95709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95709</v>
+        <v>95710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95712</v>
+        <v>95720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32497-2025 artfynd.xlsx
+++ b/artfynd/A 32497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735459</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735461</v>
       </c>
       <c r="B3" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127735460</v>
       </c>
       <c r="B4" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
